--- a/numerical-workflows/v2/framework/04_数值文档/节奏/开放节奏总览_数值文档.xlsx
+++ b/numerical-workflows/v2/framework/04_数值文档/节奏/开放节奏总览_数值文档.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读导航" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="开启节奏" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="主角日程" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="新手流程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="养成进度预估" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="缺口追踪" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读导航" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开启节奏" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主角日程" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新手流程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="养成进度预估" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="缺口追踪" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D:\Vgame_design\output\numerical-production-workflow-v2\runs\20260825-113023-390463\framework-v2\节奏\生成_开启节奏总览.xlsx</t>
+          <t>D:\Vgame_design\output\numerical-production-workflow-v2\runs\20260905-120414-220437\framework-v2\节奏\生成_开启节奏总览.xlsx</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D:\Vgame_design\output\numerical-production-workflow-v2\runs\20260825-113023-390463\Vgame新手引导以及开启节奏.xlsx</t>
+          <t>D:\Vgame_design\output\numerical-production-workflow-v2\runs\20260905-120414-220437\Vgame新手引导以及开启节奏.xlsx</t>
         </is>
       </c>
     </row>
